--- a/outputs/또래퍼센타일_전달패키지/02_또래등수_산식_v1.0.0.xlsx
+++ b/outputs/또래퍼센타일_전달패키지/02_또래등수_산식_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-metrics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC16B98-1698-464D-A1FF-4DBE9D5505BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97658EE6-5F81-4DB2-B033-5F7CD76F633D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4180" yWindow="4180" windowWidth="28800" windowHeight="15370" activeTab="1" xr2:uid="{04B47D0B-056A-43FF-A045-ABFFA5343EB3}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3321" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3325" uniqueCount="530">
   <si>
     <t>체질량지수 분포 · 국민건강보험공단 건강검진통계 2024 (KOSIS, 전국) · 단위 kg/m²</t>
   </si>
@@ -1518,15 +1518,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>② 키·체중 (국민건강영양조사 2022~2024 백분위표 보간 · 좋고 나쁨 없음)</t>
-  </si>
-  <si>
-    <t>큰 순 상위 %</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
     <t>kg</t>
   </si>
   <si>
@@ -1572,9 +1563,6 @@
     <t>키·체중·BMI·허리둘레는 K_영양조사 시트(국민건강영양조사 2022~2024 원시자료, 성인 17,262명, 가중 백분위 p1~p99)를 기준으로 계산: k = 내 값이 넘는 마지막 백분위, P = k + (x − p_k)/(p_k+1 − p_k). p1 미만은 1, p99 이상은 99. 이 p1~p99가 "내 집단·항목의 경계값 99개"</t>
   </si>
   <si>
-    <t>키·체중은 방향이 없으므로 "큰 순 상위 %"로만 표시하고 종합에서 제외. BMI·허리둘레는 P열에 건강검진 구간표 기준 P를 참고로 같이 둠(두 값이 크게 다르면 구간 보간 오차). M_신장체중 시트(인체치수조사 2020)는 참고용으로 유지</t>
-  </si>
-  <si>
     <t>분포표(D_ 시트)는 KOSIS 건강검진통계 2024 "연령별 ○○ 분포 현황"의 전국 인원수. 양끝 개방 구간(예: 180 이상)의 바깥 경계는 각 시트 3~4행의 가정값(파란색)</t>
   </si>
   <si>
@@ -1585,9 +1573,6 @@
   </si>
   <si>
     <t>개발 규격: outputs/mai-report-metrics/maiReport_또래퍼센타일_산출규격.html (PCT-001). 이 표의 G~J 열 로직이 규격 4.3~4.6절과 대응</t>
-  </si>
-  <si>
-    <t>발행 상태: v1.0.1 · 2026-10-06</t>
   </si>
   <si>
     <t>읽는 법</t>
@@ -1633,6 +1618,43 @@
   </si>
   <si>
     <t>안내</t>
+  </si>
+  <si>
+    <t>② 키·체중 (국민건강영양조사 2022~2024 백분위표 보간 · 키는 큰 쪽이 1등, 체중은 가벼운 쪽이 1등 · 종합 제외)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방향</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>또래 상위 % (rank)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>high</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>low</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>발행 상태: v1.0.2 · 2026-10-06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키·체중 방향</t>
+  </si>
+  <si>
+    <t>키는 큰 쪽이 1등(rank = 100 − P), 체중은 가벼운 쪽이 1등(rank = P)으로 정함. 구간 라벨 추가. 종합에는 여전히 넣지 않음</t>
+  </si>
+  <si>
+    <t>입력_결과 30~31행</t>
+  </si>
+  <si>
+    <t>키·체중은 종합에서 제외하되 순서는 정함: 키는 큰 쪽이 1등(rank = 100 − P, "또래 상위 N %" = 큰 순), 체중은 가벼운 쪽이 1등(rank = P). BMI·허리둘레는 P열에 건강검진 구간표 기준 P를 참고로 같이 둠. M_신장체중 시트(인체치수조사 2020)는 참고용으로 유지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2135,7 +2157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D98A01A4-C390-4F47-9990-64BDBF04BA54}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="2" width="14.58203125" customWidth="1"/>
@@ -2153,7 +2175,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>509</v>
+        <v>525</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2167,7 +2189,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -2175,7 +2197,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -2183,7 +2205,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -2197,7 +2219,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -2205,16 +2227,16 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="4" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>192</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2222,10 +2244,10 @@
         <v>46279</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>226</v>
@@ -2236,13 +2258,13 @@
         <v>46301</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2250,13 +2272,27 @@
         <v>46301</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>524</v>
+        <v>519</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="17">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>528</v>
       </c>
     </row>
   </sheetData>
@@ -60430,7 +60466,7 @@
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="3" t="s">
-        <v>486</v>
+        <v>520</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -60462,19 +60498,21 @@
         <v>435</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>436</v>
+        <v>521</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4" t="s">
         <v>438</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>487</v>
+        <v>522</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="J29" s="4"/>
+      <c r="J29" s="4" t="s">
+        <v>441</v>
+      </c>
       <c r="K29" s="4" t="s">
         <v>442</v>
       </c>
@@ -60502,7 +60540,7 @@
         <v>172</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>488</v>
+        <v>523</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="9">
@@ -60517,10 +60555,13 @@
         <f>IF(H30="","",MAX(1,MIN(99,ROUND(H30,0))))</f>
         <v>58</v>
       </c>
-      <c r="J30" s="1"/>
+      <c r="J30" s="1" t="str">
+        <f>IF(I30="","",IF(I30&lt;=25,"또래보다 큰 편",IF(I30&lt;=60,"또래 수준",IF(I30&lt;=85,"또래보다 작은 편","또래 하위 15% (작음)"))))</f>
+        <v>또래 수준</v>
+      </c>
       <c r="K30" s="1" t="str">
-        <f>IF(D30="","",IF(N30="","해당 연령·성별 행 없음","또래 평균 "&amp;TEXT(INDEX(K_영양조사!$F$4:$F$107,N30),"0.0")&amp;" · 표준편차 "&amp;TEXT(INDEX(K_영양조사!$G$4:$G$107,N30),"0.0")&amp;" · n="&amp;INDEX(K_영양조사!$E$4:$E$107,N30)&amp;" · 종합 제외"))</f>
-        <v>또래 평균 173.1 · 표준편차 5.7 · n=567 · 종합 제외</v>
+        <f>IF(D30="","",IF(N30="","해당 연령·성별 행 없음","또래 평균 "&amp;TEXT(INDEX(K_영양조사!$F$4:$F$107,N30),"0.0")&amp;" · 표준편차 "&amp;TEXT(INDEX(K_영양조사!$G$4:$G$107,N30),"0.0")&amp;" · n="&amp;INDEX(K_영양조사!$E$4:$E$107,N30)&amp;" · 큰 순 · 종합 제외"))</f>
+        <v>또래 평균 173.1 · 표준편차 5.7 · n=567 · 큰 순 · 종합 제외</v>
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -60542,13 +60583,13 @@
         <v>484</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D31" s="12">
         <v>72.5</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>488</v>
+        <v>524</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="9">
@@ -60556,17 +60597,20 @@
         <v>36.249999999999993</v>
       </c>
       <c r="H31" s="9">
-        <f>IF(G31="","",100-G31)</f>
-        <v>63.750000000000007</v>
+        <f>IF(G31="","",G31)</f>
+        <v>36.249999999999993</v>
       </c>
       <c r="I31" s="16">
         <f>IF(H31="","",MAX(1,MIN(99,ROUND(H31,0))))</f>
-        <v>64</v>
-      </c>
-      <c r="J31" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="J31" s="1" t="str">
+        <f>IF(I31="","",IF(I31&lt;=25,"또래보다 가벼운 편",IF(I31&lt;=60,"또래 수준",IF(I31&lt;=85,"또래보다 무거운 편","또래 하위 15% (무거움)"))))</f>
+        <v>또래 수준</v>
+      </c>
       <c r="K31" s="1" t="str">
-        <f>IF(D31="","",IF(N31="","해당 연령·성별 행 없음","또래 평균 "&amp;TEXT(INDEX(K_영양조사!$F$4:$F$107,N31),"0.0")&amp;" · 표준편차 "&amp;TEXT(INDEX(K_영양조사!$G$4:$G$107,N31),"0.0")&amp;" · n="&amp;INDEX(K_영양조사!$E$4:$E$107,N31)&amp;" · 종합 제외"))</f>
-        <v>또래 평균 76.9 · 표준편차 12.3 · n=568 · 종합 제외</v>
+        <f>IF(D31="","",IF(N31="","해당 연령·성별 행 없음","또래 평균 "&amp;TEXT(INDEX(K_영양조사!$F$4:$F$107,N31),"0.0")&amp;" · 표준편차 "&amp;TEXT(INDEX(K_영양조사!$G$4:$G$107,N31),"0.0")&amp;" · n="&amp;INDEX(K_영양조사!$E$4:$E$107,N31)&amp;" · 가벼운 순 · 종합 제외"))</f>
+        <v>또래 평균 76.9 · 표준편차 12.3 · n=568 · 가벼운 순 · 종합 제외</v>
       </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -60600,7 +60644,7 @@
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="3" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -60620,7 +60664,7 @@
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B34" s="1">
         <f ca="1">COUNT(H12:H26)</f>
@@ -60643,7 +60687,7 @@
     </row>
     <row r="35" spans="1:16">
       <c r="A35" s="1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B35" s="1">
         <f ca="1">COUNTIF(H12:H26,"&gt;50")</f>
@@ -60666,7 +60710,7 @@
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="1" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B36" s="9">
         <f ca="1">IF(COUNT(H12:H26)&lt;3,"",AVERAGE(H12:H26))</f>
@@ -60689,7 +60733,7 @@
     </row>
     <row r="37" spans="1:16">
       <c r="A37" s="1" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B37" s="1" t="str">
         <f ca="1">IF(B36="","항목 3개 미만",IF(B36&lt;=25,"또래보다 좋음",IF(B36&lt;=60,"또래 수준",IF(B36&lt;=85,"또래보다 나쁨","또래 하위 15%"))))</f>
@@ -60712,7 +60756,7 @@
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="1" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B38" s="1" t="str">
         <f ca="1">IFERROR(INDEX($A$12:$A$26,MATCH(LARGE($H$12:$H$26,1),$H$12:$H$26,0)),"")</f>
@@ -60759,7 +60803,7 @@
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="3" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -60779,7 +60823,7 @@
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="1" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -60799,7 +60843,7 @@
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="1" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -60819,7 +60863,7 @@
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="1" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -60839,7 +60883,7 @@
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="1" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -60859,7 +60903,7 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="1" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -60879,7 +60923,7 @@
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="1" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -60899,7 +60943,7 @@
     </row>
     <row r="47" spans="1:16">
       <c r="A47" s="1" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -60919,7 +60963,7 @@
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="1" t="s">
-        <v>504</v>
+        <v>529</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -60939,7 +60983,7 @@
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="1" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -60959,7 +61003,7 @@
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="1" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -60979,7 +61023,7 @@
     </row>
     <row r="51" spans="1:16">
       <c r="A51" s="1" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -60999,7 +61043,7 @@
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
